--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_44.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5279433.938299382</v>
+        <v>5239092.679461312</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645784</v>
+        <v>6767152.318645787</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645784</v>
+        <v>6767152.318645787</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517482</v>
+        <v>2916902.906517487</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517482</v>
+        <v>2916902.906517487</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42482734.4916698</v>
+        <v>42482734.49166981</v>
       </c>
     </row>
   </sheetData>
@@ -657,31 +657,31 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>102.948788614285</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
         <v>404.3632896068686</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>100.6192915779629</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>634.7678887921559</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>97.12488247690055</v>
+        <v>313.1545016101225</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
@@ -693,10 +693,10 @@
         <v>194.5855355810472</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P2" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>370.9706110579117</v>
@@ -705,7 +705,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>57.72562438342279</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>547.2737972923793</v>
@@ -796,7 +796,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>90.09876729325134</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -848,7 +848,7 @@
         <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
-        <v>141.974997417455</v>
+        <v>171.1850752716849</v>
       </c>
       <c r="O4" t="n">
         <v>240.445564079015</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>297.3920501269246</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -897,43 +897,43 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>353.8273874425797</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H5" t="n">
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>93.56939138541435</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>418.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>611.1455837021076</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
       </c>
       <c r="M5" t="n">
-        <v>814</v>
+        <v>297.9910820919849</v>
       </c>
       <c r="N5" t="n">
         <v>194.5855355810472</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>216.0296191332252</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q5" t="n">
         <v>370.9706110579117</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -951,16 +951,16 @@
         <v>249.2212965486107</v>
       </c>
       <c r="V5" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
@@ -1027,16 +1027,16 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>57.93598414360948</v>
       </c>
       <c r="V6" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X6" t="n">
-        <v>77.58836382881032</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>114.9691617061033</v>
+        <v>114.9691617060983</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1128,19 +1128,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>96.97292248130383</v>
       </c>
       <c r="F8" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
         <v>3.75737228701621</v>
@@ -1149,13 +1149,13 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>797.8013999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>748.0913712690559</v>
+        <v>97.12488247690055</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -1164,7 +1164,7 @@
         <v>297.9910820919849</v>
       </c>
       <c r="N8" t="n">
-        <v>194.5855355810472</v>
+        <v>814</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1173,16 +1173,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>370.9706110579162</v>
+        <v>402.5226354311147</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T8" t="n">
-        <v>280.2449731139786</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1191,13 +1191,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>638.3734759809475</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1210,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>109.78793748572</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1264,13 +1264,13 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2103597601867477</v>
+        <v>125.0582359398687</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617061012</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>320.9396782847081</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1368,16 +1368,16 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>165.5148171418603</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>6.541077446123326</v>
       </c>
       <c r="S11" t="n">
         <v>269.8481678023229</v>
@@ -1425,7 +1425,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>413.3734759809475</v>
@@ -1611,16 +1611,16 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>71.22605108397006</v>
+        <v>67.57968198731129</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1799,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>53.74128073011011</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.97841917455702</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>125.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>124.3267636724302</v>
+        <v>124.7573722870162</v>
       </c>
       <c r="H17" t="n">
         <v>129.0096587035274</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T17" t="n">
         <v>307.6755817285639</v>
@@ -2039,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="Q19" t="n">
-        <v>338.6387678008247</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         <v>202.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>170.0439696284079</v>
+        <v>170.4745782429939</v>
       </c>
       <c r="D20" t="n">
         <v>131.3391557398498</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T20" t="n">
         <v>307.6755817285639</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="Q25" t="n">
         <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>339.4016293563777</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>185.3391557398498</v>
@@ -2565,10 +2565,10 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>155.1765470578291</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>9.378975142022384</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,10 +2601,10 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
         <v>424.2212965486107</v>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2738,13 +2738,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>142.2291713307485</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2756,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>142.8671017301167</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2790,22 +2790,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>189.411675845388</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2847,10 +2847,10 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>404.8510241668239</v>
+        <v>56.69212141290342</v>
       </c>
       <c r="W29" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>367.2818334606677</v>
@@ -3048,13 +3048,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>377.7382696589756</v>
+        <v>757.6173000000412</v>
       </c>
       <c r="K32" t="n">
-        <v>351.8156858381437</v>
+        <v>10.23281455293388</v>
       </c>
       <c r="L32" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>256.9910820920268</v>
@@ -3063,7 +3063,7 @@
         <v>153.5855355810893</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>734.7038409438795</v>
       </c>
       <c r="P32" t="n">
         <v>773.0000000000421</v>
@@ -3212,28 +3212,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>298.1276103624053</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>433.5163175103893</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I35" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>757.6173000000483</v>
+        <v>377.7382696589829</v>
       </c>
       <c r="K35" t="n">
-        <v>10.23281455315785</v>
+        <v>727.1079320762591</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>397.7077537618483</v>
       </c>
       <c r="M35" t="n">
         <v>256.991082092034</v>
@@ -3300,16 +3300,16 @@
         <v>153.5855355810966</v>
       </c>
       <c r="O35" t="n">
-        <v>734.7038409438826</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000493</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>329.970611057961</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S35" t="n">
         <v>203.8481678023229</v>
@@ -3449,25 +3449,25 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>228.8671215550752</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>70.05053078766994</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3504,7 +3504,7 @@
         <v>158.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>119.3391557398498</v>
+        <v>127.7957471252641</v>
       </c>
       <c r="E38" t="n">
         <v>113.3632896068686</v>
@@ -3525,10 +3525,10 @@
         <v>377.7382696589902</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320762786</v>
+        <v>56.12488247690067</v>
       </c>
       <c r="L38" t="n">
-        <v>397.7077537618541</v>
+        <v>727.1079320759846</v>
       </c>
       <c r="M38" t="n">
         <v>256.9910820920413</v>
@@ -3540,13 +3540,13 @@
         <v>773.0000000000566</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>341.5828712849589</v>
       </c>
       <c r="Q38" t="n">
         <v>329.9706110579683</v>
       </c>
       <c r="R38" t="n">
-        <v>8.456591385414804</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3701,13 +3701,13 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>433.5163175104163</v>
+        <v>372.3421690554655</v>
       </c>
       <c r="R40" t="n">
         <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>236.4745782429939</v>
@@ -3753,7 +3753,7 @@
         <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3792,19 +3792,19 @@
         <v>373.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>436.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>416.8510241668239</v>
+        <v>157.0237892535027</v>
       </c>
       <c r="W41" t="n">
-        <v>425.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>20.18623035969629</v>
+        <v>379.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>298.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>80.28438397411497</v>
+        <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>253.5639999646113</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>219.3731429098285</v>
+        <v>98.40326768090227</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>67.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>15.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>137.8763431805457</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>13.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3975,10 +3975,10 @@
         <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>36.31057358334157</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -4020,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>219.1384424760049</v>
+        <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>399.6755817285639</v>
@@ -4035,7 +4035,7 @@
         <v>442.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>451.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>405.2818334606677</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>16.55705513387049</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>75.52035840552284</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>23.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1199.993207924634</v>
+        <v>1604.033611965038</v>
       </c>
       <c r="C2" t="n">
-        <v>745.9784824266604</v>
+        <v>1554.059290507469</v>
       </c>
       <c r="D2" t="n">
-        <v>641.9898070586958</v>
+        <v>1543.615698851055</v>
       </c>
       <c r="E2" t="n">
-        <v>233.5420397790304</v>
+        <v>1135.16793157139</v>
       </c>
       <c r="F2" t="n">
-        <v>228.6030208820488</v>
+        <v>726.1885086340038</v>
       </c>
       <c r="G2" t="n">
-        <v>224.8076953396081</v>
+        <v>318.3527790511591</v>
       </c>
       <c r="H2" t="n">
         <v>216.7171309926107</v>
@@ -4321,22 +4321,22 @@
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>229.8003143513577</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>937.5543724554985</v>
+        <v>937.554372455499</v>
       </c>
       <c r="L2" t="n">
-        <v>921.1921502332762</v>
+        <v>921.1921502332766</v>
       </c>
       <c r="M2" t="n">
-        <v>1426.051057211069</v>
+        <v>1426.05105721107</v>
       </c>
       <c r="N2" t="n">
-        <v>2035.360011169607</v>
+        <v>2035.360011169608</v>
       </c>
       <c r="O2" t="n">
-        <v>2841.220011169607</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P2" t="n">
         <v>2824.857788947385</v>
@@ -4348,25 +4348,25 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2502.740639767053</v>
+        <v>2906.781043807457</v>
       </c>
       <c r="T2" t="n">
-        <v>2314.179446101837</v>
+        <v>2718.219850142241</v>
       </c>
       <c r="U2" t="n">
-        <v>2062.440762719402</v>
+        <v>2466.481166759806</v>
       </c>
       <c r="V2" t="n">
-        <v>1830.268011035741</v>
+        <v>2234.308415076146</v>
       </c>
       <c r="W2" t="n">
-        <v>1589.486722166097</v>
+        <v>1993.527126206502</v>
       </c>
       <c r="X2" t="n">
-        <v>1395.262647963403</v>
+        <v>1799.303052003807</v>
       </c>
       <c r="Y2" t="n">
-        <v>1282.820796768649</v>
+        <v>1686.861200809053</v>
       </c>
     </row>
     <row r="3">
@@ -4421,22 +4421,22 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1162.243708870129</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>609.4418934232809</v>
+        <v>667.7506049216878</v>
       </c>
       <c r="S3" t="n">
-        <v>138.1651257822594</v>
+        <v>196.4738372806663</v>
       </c>
       <c r="T3" t="n">
-        <v>132.7532417241646</v>
+        <v>191.0619532225715</v>
       </c>
       <c r="U3" t="n">
-        <v>132.5407571179154</v>
+        <v>190.8494686163223</v>
       </c>
       <c r="V3" t="n">
-        <v>117.8835175305213</v>
+        <v>176.1922290289282</v>
       </c>
       <c r="W3" t="n">
         <v>85.18337317715914</v>
@@ -4455,52 +4455,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1035.355674768119</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="C4" t="n">
-        <v>1161.357680586555</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="D4" t="n">
-        <v>1274.676824711555</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="E4" t="n">
-        <v>1392.505728922968</v>
+        <v>627.6898157036027</v>
       </c>
       <c r="F4" t="n">
-        <v>1516.866701514904</v>
+        <v>752.0507882955382</v>
       </c>
       <c r="G4" t="n">
-        <v>1516.866701514904</v>
+        <v>905.4573541824234</v>
       </c>
       <c r="H4" t="n">
-        <v>1516.866701514904</v>
+        <v>1074.973939341821</v>
       </c>
       <c r="I4" t="n">
-        <v>1546.422113931137</v>
+        <v>1074.973939341821</v>
       </c>
       <c r="J4" t="n">
-        <v>1546.422113931137</v>
+        <v>1436.057679994272</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931137</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="L4" t="n">
-        <v>1522.636630943481</v>
+        <v>1522.636630943485</v>
       </c>
       <c r="M4" t="n">
-        <v>1400.786518415653</v>
+        <v>1400.786518415657</v>
       </c>
       <c r="N4" t="n">
-        <v>1257.377430115193</v>
+        <v>1227.87230096951</v>
       </c>
       <c r="O4" t="n">
-        <v>1014.503122964673</v>
+        <v>984.99799381899</v>
       </c>
       <c r="P4" t="n">
-        <v>724.1517115219688</v>
+        <v>694.6465823762856</v>
       </c>
       <c r="Q4" t="n">
-        <v>395.0211393749001</v>
+        <v>365.5160102292168</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
@@ -4512,19 +4512,19 @@
         <v>290.445934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>290.445934252978</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="V4" t="n">
-        <v>489.2673271389239</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="W4" t="n">
-        <v>661.1582453986014</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="X4" t="n">
-        <v>812.1890364227949</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="Y4" t="n">
-        <v>923.5983371018272</v>
+        <v>536.9971268912645</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>241.2847218926083</v>
+        <v>1857.446338054225</v>
       </c>
       <c r="C5" t="n">
-        <v>191.3104004350387</v>
+        <v>1807.472016596655</v>
       </c>
       <c r="D5" t="n">
-        <v>180.8668087786247</v>
+        <v>1450.070615139504</v>
       </c>
       <c r="E5" t="n">
-        <v>176.4594455393635</v>
+        <v>1041.622847859839</v>
       </c>
       <c r="F5" t="n">
-        <v>171.5204266423818</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G5" t="n">
-        <v>167.7251010999412</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H5" t="n">
-        <v>159.6345367529438</v>
+        <v>216.7171309926107</v>
       </c>
       <c r="I5" t="n">
         <v>65.12</v>
@@ -4561,19 +4561,19 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K5" t="n">
-        <v>636.5532794332917</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L5" t="n">
-        <v>620.1910572110693</v>
+        <v>1139.40388673148</v>
       </c>
       <c r="M5" t="n">
-        <v>603.828834988847</v>
+        <v>1644.262793709273</v>
       </c>
       <c r="N5" t="n">
-        <v>1213.137788947385</v>
+        <v>2253.571747667811</v>
       </c>
       <c r="O5" t="n">
-        <v>2018.997788947385</v>
+        <v>2841.220011169604</v>
       </c>
       <c r="P5" t="n">
         <v>2824.857788947385</v>
@@ -4585,25 +4585,25 @@
         <v>3256</v>
       </c>
       <c r="S5" t="n">
-        <v>2756.153365856239</v>
+        <v>3160.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>2567.592172191023</v>
+        <v>2971.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>2315.853488808588</v>
+        <v>2719.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>1679.640333084524</v>
+        <v>2487.721141165332</v>
       </c>
       <c r="W5" t="n">
-        <v>1438.85904421488</v>
+        <v>2246.939852295688</v>
       </c>
       <c r="X5" t="n">
-        <v>840.594565971781</v>
+        <v>2052.715778092993</v>
       </c>
       <c r="Y5" t="n">
-        <v>324.1123107366229</v>
+        <v>1940.273926898239</v>
       </c>
     </row>
     <row r="6">
@@ -4661,22 +4661,22 @@
         <v>1220.552420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>667.7506049216878</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>600.5142413210704</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T6" t="n">
-        <v>595.1023572629756</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>594.8898726567263</v>
+        <v>940.6215651987236</v>
       </c>
       <c r="V6" t="n">
-        <v>176.1922290289281</v>
+        <v>521.9239215709254</v>
       </c>
       <c r="W6" t="n">
-        <v>143.492084675566</v>
+        <v>85.18337317715914</v>
       </c>
       <c r="X6" t="n">
         <v>65.12</v>
@@ -4692,37 +4692,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>648.7544645575567</v>
+        <v>214.1275927604653</v>
       </c>
       <c r="C7" t="n">
-        <v>774.7564703759925</v>
+        <v>340.129598578901</v>
       </c>
       <c r="D7" t="n">
-        <v>774.7564703759925</v>
+        <v>453.4487427039011</v>
       </c>
       <c r="E7" t="n">
-        <v>892.5853745874056</v>
+        <v>453.4487427039011</v>
       </c>
       <c r="F7" t="n">
-        <v>892.5853745874056</v>
+        <v>577.8097152958367</v>
       </c>
       <c r="G7" t="n">
-        <v>1045.991940474291</v>
+        <v>684.3244752463361</v>
       </c>
       <c r="H7" t="n">
-        <v>1215.508525633689</v>
+        <v>853.8410604057336</v>
       </c>
       <c r="I7" t="n">
-        <v>1436.641404569772</v>
+        <v>1074.973939341817</v>
       </c>
       <c r="J7" t="n">
-        <v>1546.422113931141</v>
+        <v>1436.057679994268</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="L7" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931136</v>
       </c>
       <c r="M7" t="n">
         <v>1430.29164756134</v>
@@ -4746,22 +4746,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>290.445934252978</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="U7" t="n">
-        <v>536.9971268912645</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="V7" t="n">
-        <v>536.9971268912645</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="W7" t="n">
-        <v>536.9971268912645</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="X7" t="n">
-        <v>536.9971268912645</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="Y7" t="n">
-        <v>536.9971268912645</v>
+        <v>102.3702550941731</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1358.891397260877</v>
+        <v>391.9123998438259</v>
       </c>
       <c r="C8" t="n">
-        <v>904.876671762903</v>
+        <v>341.9380783862563</v>
       </c>
       <c r="D8" t="n">
-        <v>490.392676066085</v>
+        <v>331.4944867298424</v>
       </c>
       <c r="E8" t="n">
-        <v>485.9853128268237</v>
+        <v>233.5420397790304</v>
       </c>
       <c r="F8" t="n">
-        <v>77.00588988943801</v>
+        <v>228.6030208820488</v>
       </c>
       <c r="G8" t="n">
-        <v>73.21056434699739</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H8" t="n">
-        <v>65.12</v>
+        <v>216.7171309926107</v>
       </c>
       <c r="I8" t="n">
         <v>65.12</v>
@@ -4798,49 +4798,49 @@
         <v>65.12</v>
       </c>
       <c r="K8" t="n">
-        <v>115.3321502332768</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L8" t="n">
-        <v>98.96992801105449</v>
+        <v>756.5118358819186</v>
       </c>
       <c r="M8" t="n">
-        <v>603.8288349888475</v>
+        <v>1261.370742859712</v>
       </c>
       <c r="N8" t="n">
-        <v>1213.137788947386</v>
+        <v>1245.008520637489</v>
       </c>
       <c r="O8" t="n">
-        <v>2018.997788947386</v>
+        <v>2050.868520637489</v>
       </c>
       <c r="P8" t="n">
-        <v>2824.857788947386</v>
+        <v>2856.72852063749</v>
       </c>
       <c r="Q8" t="n">
         <v>3256</v>
       </c>
       <c r="R8" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>3160.193769896644</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T8" t="n">
-        <v>2877.118039478483</v>
+        <v>2314.179446101837</v>
       </c>
       <c r="U8" t="n">
-        <v>2625.379356096048</v>
+        <v>2062.440762719402</v>
       </c>
       <c r="V8" t="n">
-        <v>2393.206604412388</v>
+        <v>1830.268011035741</v>
       </c>
       <c r="W8" t="n">
-        <v>2152.425315542744</v>
+        <v>1185.446318125693</v>
       </c>
       <c r="X8" t="n">
-        <v>1958.201241340049</v>
+        <v>991.2222439229986</v>
       </c>
       <c r="Y8" t="n">
-        <v>1845.759390145295</v>
+        <v>474.7399886878405</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527.4691155388108</v>
+        <v>630.5730132457184</v>
       </c>
       <c r="C9" t="n">
-        <v>416.5722089875784</v>
+        <v>630.5730132457184</v>
       </c>
       <c r="D9" t="n">
-        <v>65.12</v>
+        <v>630.5730132457184</v>
       </c>
       <c r="E9" t="n">
-        <v>65.12</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="F9" t="n">
-        <v>65.12</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="G9" t="n">
-        <v>65.12</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="H9" t="n">
-        <v>65.12</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="I9" t="n">
         <v>65.12</v>
@@ -4895,31 +4895,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1220.552420368536</v>
+        <v>1045.724879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1071.791008962092</v>
+        <v>896.9634684666578</v>
       </c>
       <c r="S9" t="n">
-        <v>1004.554645361474</v>
+        <v>829.7271048660403</v>
       </c>
       <c r="T9" t="n">
-        <v>999.1427613033796</v>
+        <v>824.3152208079456</v>
       </c>
       <c r="U9" t="n">
-        <v>998.9302766971304</v>
+        <v>697.9937703636338</v>
       </c>
       <c r="V9" t="n">
-        <v>984.2730371097363</v>
+        <v>683.3365307762397</v>
       </c>
       <c r="W9" t="n">
-        <v>547.53248871597</v>
+        <v>650.6363864228775</v>
       </c>
       <c r="X9" t="n">
-        <v>527.4691155388108</v>
+        <v>630.5730132457184</v>
       </c>
       <c r="Y9" t="n">
-        <v>527.4691155388108</v>
+        <v>630.5730132457184</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>810.0297405151414</v>
+        <v>664.6433636224958</v>
       </c>
       <c r="C10" t="n">
-        <v>936.0317463335772</v>
+        <v>790.6453694409316</v>
       </c>
       <c r="D10" t="n">
-        <v>1049.350890458577</v>
+        <v>790.6453694409316</v>
       </c>
       <c r="E10" t="n">
-        <v>1167.17979466999</v>
+        <v>908.4742736523447</v>
       </c>
       <c r="F10" t="n">
-        <v>1291.540767261926</v>
+        <v>908.4742736523447</v>
       </c>
       <c r="G10" t="n">
-        <v>1444.947333148811</v>
+        <v>1061.88083953923</v>
       </c>
       <c r="H10" t="n">
-        <v>1546.422113931145</v>
+        <v>1231.397424698628</v>
       </c>
       <c r="I10" t="n">
-        <v>1546.422113931145</v>
+        <v>1452.530303634711</v>
       </c>
       <c r="J10" t="n">
-        <v>1546.422113931145</v>
+        <v>1546.422113931139</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931145</v>
+        <v>1546.422113931139</v>
       </c>
       <c r="L10" t="n">
-        <v>1546.422113931145</v>
+        <v>1546.422113931139</v>
       </c>
       <c r="M10" t="n">
-        <v>1424.572001403317</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1251.65778395717</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O10" t="n">
-        <v>1008.78347680665</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P10" t="n">
-        <v>718.4320653639456</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>389.3014932168769</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
       </c>
       <c r="S10" t="n">
-        <v>65.12</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="T10" t="n">
-        <v>65.12</v>
+        <v>290.445934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>65.12</v>
+        <v>290.445934252978</v>
       </c>
       <c r="V10" t="n">
-        <v>263.941392885946</v>
+        <v>290.445934252978</v>
       </c>
       <c r="W10" t="n">
-        <v>435.8323111456234</v>
+        <v>290.445934252978</v>
       </c>
       <c r="X10" t="n">
-        <v>586.8631021698169</v>
+        <v>441.4767252771715</v>
       </c>
       <c r="Y10" t="n">
-        <v>698.2724028488492</v>
+        <v>552.8860259562038</v>
       </c>
     </row>
     <row r="11">
@@ -5008,16 +5008,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>417.1649250963513</v>
+        <v>845.6382034286696</v>
       </c>
       <c r="C11" t="n">
-        <v>249.9782411146742</v>
+        <v>618.8962052034233</v>
       </c>
       <c r="D11" t="n">
-        <v>249.9782411146742</v>
+        <v>431.6849367793326</v>
       </c>
       <c r="E11" t="n">
-        <v>249.9782411146742</v>
+        <v>431.6849367793326</v>
       </c>
       <c r="F11" t="n">
         <v>249.9782411146742</v>
@@ -5035,16 +5035,16 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>1166.135479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="L11" t="n">
-        <v>1166.135479385524</v>
+        <v>1693.331756443634</v>
       </c>
       <c r="M11" t="n">
-        <v>1676.984308114459</v>
+        <v>2204.180585172569</v>
       </c>
       <c r="N11" t="n">
-        <v>2290.204627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="O11" t="n">
         <v>2817.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>3256</v>
       </c>
       <c r="R11" t="n">
-        <v>3229.860001183541</v>
+        <v>3249.392851064522</v>
       </c>
       <c r="S11" t="n">
-        <v>2957.286094312508</v>
+        <v>2976.818944193489</v>
       </c>
       <c r="T11" t="n">
-        <v>2591.957223879615</v>
+        <v>2611.490073760596</v>
       </c>
       <c r="U11" t="n">
-        <v>2163.450863729503</v>
+        <v>2182.983713610484</v>
       </c>
       <c r="V11" t="n">
-        <v>1754.510435278166</v>
+        <v>2182.983713610484</v>
       </c>
       <c r="W11" t="n">
-        <v>1336.961469640845</v>
+        <v>1765.434747973163</v>
       </c>
       <c r="X11" t="n">
-        <v>965.9697186704734</v>
+        <v>1394.442997002792</v>
       </c>
       <c r="Y11" t="n">
-        <v>676.7601907080427</v>
+        <v>1105.233469040361</v>
       </c>
     </row>
     <row r="12">
@@ -5111,13 +5111,13 @@
         <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>419.6213981428639</v>
+        <v>215.7971006891144</v>
       </c>
       <c r="K12" t="n">
-        <v>831.5642142372474</v>
+        <v>627.7399167834978</v>
       </c>
       <c r="L12" t="n">
-        <v>1325.664675832448</v>
+        <v>1121.840378378698</v>
       </c>
       <c r="M12" t="n">
         <v>1430.670920121557</v>
@@ -5254,13 +5254,13 @@
         <v>291.9779198897361</v>
       </c>
       <c r="E14" t="n">
-        <v>137.0655061454243</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="F14" t="n">
-        <v>65.12</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="G14" t="n">
-        <v>65.12</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="H14" t="n">
         <v>65.12</v>
@@ -5269,19 +5269,19 @@
         <v>65.12</v>
       </c>
       <c r="J14" t="n">
-        <v>456.4291130376557</v>
+        <v>177.7653900957659</v>
       </c>
       <c r="K14" t="n">
-        <v>1166.135479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="L14" t="n">
-        <v>1166.135479385524</v>
+        <v>1693.331756443634</v>
       </c>
       <c r="M14" t="n">
-        <v>1676.984308114459</v>
+        <v>2204.180585172569</v>
       </c>
       <c r="N14" t="n">
-        <v>2290.204627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="O14" t="n">
         <v>2817.400904947332</v>
@@ -5348,7 +5348,7 @@
         <v>98.65487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>222.6113981428639</v>
+        <v>387.1477067497204</v>
       </c>
       <c r="K15" t="n">
         <v>576.3405228441038</v>
@@ -5357,7 +5357,7 @@
         <v>1096.180984439304</v>
       </c>
       <c r="M15" t="n">
-        <v>1182.261526182163</v>
+        <v>1430.751526182163</v>
       </c>
       <c r="N15" t="n">
         <v>1564.031810789731</v>
@@ -5442,13 +5442,13 @@
         <v>599.0397446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>599.0397446017254</v>
+        <v>544.7556226521192</v>
       </c>
       <c r="P16" t="n">
-        <v>599.0397446017254</v>
+        <v>544.7556226521192</v>
       </c>
       <c r="Q16" t="n">
-        <v>545.5261898799506</v>
+        <v>65.12</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>879.6685602764463</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C17" t="n">
-        <v>707.4720165966545</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D17" t="n">
-        <v>574.8062027180183</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E17" t="n">
-        <v>448.1766172565348</v>
+        <v>448.6115754530863</v>
       </c>
       <c r="F17" t="n">
-        <v>321.0153761373309</v>
+        <v>321.4503343338824</v>
       </c>
       <c r="G17" t="n">
         <v>195.4327865692196</v>
@@ -5506,25 +5506,25 @@
         <v>65.12</v>
       </c>
       <c r="J17" t="n">
-        <v>456.4291130376557</v>
+        <v>177.7653900957659</v>
       </c>
       <c r="K17" t="n">
-        <v>1166.135479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="L17" t="n">
-        <v>1971.995479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="M17" t="n">
-        <v>2482.844308114459</v>
+        <v>1398.320585172569</v>
       </c>
       <c r="N17" t="n">
-        <v>3096.064627889222</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5533,25 +5533,25 @@
         <v>3256</v>
       </c>
       <c r="S17" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V17" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W17" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X17" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y17" t="n">
-        <v>1084.718371342683</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="18">
@@ -5600,7 +5600,7 @@
         <v>930.2355021828749</v>
       </c>
       <c r="O18" t="n">
-        <v>1323.391838231026</v>
+        <v>1445.487953866594</v>
       </c>
       <c r="P18" t="n">
         <v>1712.131182700533</v>
@@ -5682,10 +5682,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P19" t="n">
-        <v>859.3027230120967</v>
+        <v>516.472794369291</v>
       </c>
       <c r="Q19" t="n">
-        <v>517.2433615971223</v>
+        <v>65.12</v>
       </c>
       <c r="R19" t="n">
         <v>65.12</v>
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>879.6685602764463</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C20" t="n">
         <v>707.906974793206</v>
@@ -5755,7 +5755,7 @@
         <v>1676.984308114459</v>
       </c>
       <c r="N20" t="n">
-        <v>2290.204627889222</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O20" t="n">
         <v>2817.400904947332</v>
@@ -5770,25 +5770,25 @@
         <v>3256</v>
       </c>
       <c r="S20" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V20" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W20" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y20" t="n">
-        <v>1084.718371342683</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="21">
@@ -5822,22 +5822,22 @@
         <v>126.374877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>250.3313981428639</v>
+        <v>526.5413981428638</v>
       </c>
       <c r="K21" t="n">
-        <v>439.5242142372473</v>
+        <v>869.8480986016793</v>
       </c>
       <c r="L21" t="n">
-        <v>710.8746758324473</v>
+        <v>1141.198560196879</v>
       </c>
       <c r="M21" t="n">
-        <v>796.9552175753066</v>
+        <v>1227.279101939739</v>
       </c>
       <c r="N21" t="n">
-        <v>930.2355021828749</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1323.391838231026</v>
+        <v>1599.601838231026</v>
       </c>
       <c r="P21" t="n">
         <v>1712.131182700533</v>
@@ -5986,13 +5986,13 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1971.995479385524</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>2482.844308114459</v>
+        <v>1676.984308114459</v>
       </c>
       <c r="N23" t="n">
-        <v>2817.400904947332</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="O23" t="n">
         <v>2817.400904947332</v>
@@ -6156,10 +6156,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>859.3027230120967</v>
+        <v>516.472794369291</v>
       </c>
       <c r="Q25" t="n">
-        <v>407.9499286428058</v>
+        <v>65.12</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1180.277230362708</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="C26" t="n">
-        <v>953.5352321374614</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="D26" t="n">
-        <v>766.3239637133707</v>
+        <v>614.7584502463829</v>
       </c>
       <c r="E26" t="n">
-        <v>585.1489237064327</v>
+        <v>433.5834102394449</v>
       </c>
       <c r="F26" t="n">
-        <v>403.4422280417742</v>
+        <v>251.8767145747865</v>
       </c>
       <c r="G26" t="n">
-        <v>246.6982411146742</v>
+        <v>71.31371226466908</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6223,13 +6223,13 @@
         <v>1162.855479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1162.855479385524</v>
+        <v>1529.331756443634</v>
       </c>
       <c r="M26" t="n">
-        <v>1673.704308114459</v>
+        <v>2040.180585172569</v>
       </c>
       <c r="N26" t="n">
-        <v>2286.924627889222</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="O26" t="n">
         <v>2653.400904947332</v>
@@ -6244,25 +6244,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>3065.860001183541</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>3065.860001183541</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2637.353641033429</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>2228.413212582092</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1810.864246944771</v>
+        <v>1172.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1439.872495974399</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>1439.872495974399</v>
+        <v>801.9697186704736</v>
       </c>
     </row>
     <row r="27">
@@ -6308,10 +6308,10 @@
         <v>1631.215217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1987.245502182875</v>
+        <v>1783.421204729126</v>
       </c>
       <c r="O27" t="n">
-        <v>2449.037953866594</v>
+        <v>2245.213656412845</v>
       </c>
       <c r="P27" t="n">
         <v>2580.493000882351</v>
@@ -6357,49 +6357,49 @@
         <v>174.1515880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>174.1515880782802</v>
+        <v>113.0038930726686</v>
       </c>
       <c r="E28" t="n">
-        <v>174.1515880782802</v>
+        <v>113.0038930726686</v>
       </c>
       <c r="F28" t="n">
-        <v>174.1515880782802</v>
+        <v>113.0038930726686</v>
       </c>
       <c r="G28" t="n">
-        <v>174.1515880782802</v>
+        <v>113.0038930726686</v>
       </c>
       <c r="H28" t="n">
-        <v>170.342369793817</v>
+        <v>109.1946747882053</v>
       </c>
       <c r="I28" t="n">
-        <v>218.2252487298999</v>
+        <v>157.0775537242883</v>
       </c>
       <c r="J28" t="n">
-        <v>406.0589893823512</v>
+        <v>344.9112943767396</v>
       </c>
       <c r="K28" t="n">
-        <v>406.0589893823512</v>
+        <v>344.9112943767396</v>
       </c>
       <c r="L28" t="n">
-        <v>205.5058296270187</v>
+        <v>344.9112943767396</v>
       </c>
       <c r="M28" t="n">
-        <v>205.5058296270187</v>
+        <v>344.9112943767396</v>
       </c>
       <c r="N28" t="n">
-        <v>61.84</v>
+        <v>344.9112943767396</v>
       </c>
       <c r="O28" t="n">
-        <v>61.84</v>
+        <v>344.9112943767396</v>
       </c>
       <c r="P28" t="n">
-        <v>61.84</v>
+        <v>344.9112943767396</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.84</v>
+        <v>344.9112943767396</v>
       </c>
       <c r="R28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="S28" t="n">
         <v>61.84</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>253.1649250963515</v>
+        <v>1022.389550081067</v>
       </c>
       <c r="C29" t="n">
-        <v>61.84</v>
+        <v>795.6475518558203</v>
       </c>
       <c r="D29" t="n">
-        <v>61.84</v>
+        <v>608.4362834317296</v>
       </c>
       <c r="E29" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="F29" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6457,16 +6457,16 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K29" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>1218.419113037656</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="M29" t="n">
-        <v>1729.267941766591</v>
+        <v>2438.974308114459</v>
       </c>
       <c r="N29" t="n">
-        <v>2342.488261541354</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="O29" t="n">
         <v>2653.400904947332</v>
@@ -6490,16 +6490,16 @@
         <v>1999.450863729503</v>
       </c>
       <c r="V29" t="n">
-        <v>1590.510435278166</v>
+        <v>1942.18609462556</v>
       </c>
       <c r="W29" t="n">
-        <v>1172.961469640845</v>
+        <v>1942.18609462556</v>
       </c>
       <c r="X29" t="n">
-        <v>801.9697186704736</v>
+        <v>1571.194343655189</v>
       </c>
       <c r="Y29" t="n">
-        <v>512.760190708043</v>
+        <v>1281.984815692758</v>
       </c>
     </row>
     <row r="30">
@@ -6545,10 +6545,10 @@
         <v>1631.215217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1987.245502182875</v>
+        <v>1783.421204729126</v>
       </c>
       <c r="O30" t="n">
-        <v>2449.037953866594</v>
+        <v>2245.213656412845</v>
       </c>
       <c r="P30" t="n">
         <v>2580.493000882351</v>
@@ -6691,19 +6691,19 @@
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>445.5561922637025</v>
+        <v>61.84</v>
       </c>
       <c r="K32" t="n">
-        <v>810.0236653847541</v>
+        <v>771.3406764391781</v>
       </c>
       <c r="L32" t="n">
-        <v>794.4855845766731</v>
+        <v>1536.610676439178</v>
       </c>
       <c r="M32" t="n">
-        <v>1300.168632968607</v>
+        <v>2042.293724831112</v>
       </c>
       <c r="N32" t="n">
-        <v>1910.301728341285</v>
+        <v>2652.42682020379</v>
       </c>
       <c r="O32" t="n">
         <v>2675.571728341327</v>
@@ -6776,16 +6776,16 @@
         <v>448.1242142372473</v>
       </c>
       <c r="L33" t="n">
-        <v>719.4746758324475</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>805.5552175753068</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>938.8355021828751</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>1177.877953866594</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P33" t="n">
         <v>1515.153000882351</v>
@@ -6831,49 +6831,49 @@
         <v>504.0986181306686</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556924</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664671054</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I34" t="n">
-        <v>756.2036690414067</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L34" t="n">
-        <v>877.9453505420606</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M34" t="n">
-        <v>645.9942279132224</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N34" t="n">
-        <v>362.9790003660659</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O34" t="n">
-        <v>61.84</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="P34" t="n">
-        <v>61.84</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.84</v>
+        <v>573.9365734181883</v>
       </c>
       <c r="R34" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S34" t="n">
         <v>61.84</v>
@@ -6904,46 +6904,46 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C35" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D35" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E35" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F35" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G35" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H35" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I35" t="n">
         <v>61.84</v>
       </c>
       <c r="J35" t="n">
-        <v>61.84</v>
+        <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>771.3406764391735</v>
+        <v>430.9405883765129</v>
       </c>
       <c r="L35" t="n">
-        <v>1536.610676439174</v>
+        <v>794.485584576666</v>
       </c>
       <c r="M35" t="n">
-        <v>2042.293724831107</v>
+        <v>1300.1686329686</v>
       </c>
       <c r="N35" t="n">
-        <v>2652.426820203786</v>
+        <v>1910.301728341278</v>
       </c>
       <c r="O35" t="n">
-        <v>2675.571728341327</v>
+        <v>1894.763647533196</v>
       </c>
       <c r="P35" t="n">
         <v>2660.033647533245</v>
@@ -6952,28 +6952,28 @@
         <v>3092</v>
       </c>
       <c r="R35" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S35" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T35" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U35" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V35" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W35" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X35" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y35" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="36">
@@ -7007,22 +7007,22 @@
         <v>134.974877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>483.6771006891146</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K36" t="n">
-        <v>672.869916783498</v>
+        <v>448.1242142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>944.220378378698</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M36" t="n">
-        <v>1030.300920121557</v>
+        <v>805.5552175753068</v>
       </c>
       <c r="N36" t="n">
-        <v>1163.581204729126</v>
+        <v>938.8355021828751</v>
       </c>
       <c r="O36" t="n">
-        <v>1402.623656412844</v>
+        <v>1177.877953866594</v>
       </c>
       <c r="P36" t="n">
         <v>1515.153000882351</v>
@@ -7092,22 +7092,22 @@
         <v>1011.831843630726</v>
       </c>
       <c r="L37" t="n">
-        <v>877.9453505420606</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="M37" t="n">
-        <v>645.9942279132224</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="N37" t="n">
-        <v>414.8153172515302</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="O37" t="n">
-        <v>61.84</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="P37" t="n">
-        <v>61.84</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.84</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R37" t="n">
         <v>61.84</v>
@@ -7131,7 +7131,7 @@
         <v>478.6599739669085</v>
       </c>
       <c r="Y37" t="n">
-        <v>482.1592746459407</v>
+        <v>482.1592746459644</v>
       </c>
     </row>
     <row r="38">
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>804.0962457457251</v>
+        <v>812.6382572461436</v>
       </c>
       <c r="C38" t="n">
-        <v>644.0209141871454</v>
+        <v>652.5629256875638</v>
       </c>
       <c r="D38" t="n">
         <v>523.4763124297214</v>
@@ -7168,19 +7168,19 @@
         <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>430.9405883765123</v>
+        <v>1154.134391781985</v>
       </c>
       <c r="L38" t="n">
-        <v>794.4855845766597</v>
+        <v>1139.5187878948</v>
       </c>
       <c r="M38" t="n">
-        <v>1300.168632968593</v>
+        <v>1645.201836286734</v>
       </c>
       <c r="N38" t="n">
-        <v>1910.301728341272</v>
+        <v>2255.334931659412</v>
       </c>
       <c r="O38" t="n">
-        <v>1894.76364753319</v>
+        <v>2239.79685085133</v>
       </c>
       <c r="P38" t="n">
         <v>2660.033647533246</v>
@@ -7189,28 +7189,28 @@
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3083.457988499581</v>
+        <v>3092</v>
       </c>
       <c r="S38" t="n">
-        <v>2877.550748295214</v>
+        <v>2886.092759795633</v>
       </c>
       <c r="T38" t="n">
-        <v>2578.888544528988</v>
+        <v>2587.430556029407</v>
       </c>
       <c r="U38" t="n">
-        <v>2217.048851045543</v>
+        <v>2225.590862545962</v>
       </c>
       <c r="V38" t="n">
-        <v>1874.775089260873</v>
+        <v>1883.317100761291</v>
       </c>
       <c r="W38" t="n">
-        <v>1523.892790290219</v>
+        <v>1532.434801790637</v>
       </c>
       <c r="X38" t="n">
-        <v>1219.567705986514</v>
+        <v>1228.109717486932</v>
       </c>
       <c r="Y38" t="n">
-        <v>997.0248446907499</v>
+        <v>1005.566856191168</v>
       </c>
     </row>
     <row r="39">
@@ -7253,16 +7253,16 @@
         <v>719.4746758324475</v>
       </c>
       <c r="M39" t="n">
-        <v>805.5552175753068</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N39" t="n">
-        <v>938.8355021828751</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O39" t="n">
-        <v>1177.877953866594</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P39" t="n">
-        <v>1578.497298336101</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q39" t="n">
         <v>1631.894528442776</v>
@@ -7299,55 +7299,55 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>486.0066123122601</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>504.0986181306959</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>509.507762255696</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E40" t="n">
-        <v>519.426666467109</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F40" t="n">
-        <v>535.8776390590446</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G40" t="n">
-        <v>581.3742049459298</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H40" t="n">
-        <v>642.9807901053274</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I40" t="n">
-        <v>756.2036690414103</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1009.377409693862</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.83184363073</v>
+        <v>877.945350542037</v>
       </c>
       <c r="M40" t="n">
-        <v>1011.83184363073</v>
+        <v>877.945350542037</v>
       </c>
       <c r="N40" t="n">
-        <v>1011.83184363073</v>
+        <v>877.945350542037</v>
       </c>
       <c r="O40" t="n">
-        <v>1011.83184363073</v>
+        <v>877.945350542037</v>
       </c>
       <c r="P40" t="n">
-        <v>1011.83184363073</v>
+        <v>877.945350542037</v>
       </c>
       <c r="Q40" t="n">
-        <v>573.9365734181883</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R40" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="S40" t="n">
         <v>61.84</v>
@@ -7368,7 +7368,7 @@
         <v>478.6599739669085</v>
       </c>
       <c r="Y40" t="n">
-        <v>482.159274645968</v>
+        <v>482.1592746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1079.844065237112</v>
+        <v>1276.823518472998</v>
       </c>
       <c r="C41" t="n">
-        <v>840.9808548906531</v>
+        <v>1037.960308126539</v>
       </c>
       <c r="D41" t="n">
-        <v>641.6483743453502</v>
+        <v>838.6278275812365</v>
       </c>
       <c r="E41" t="n">
-        <v>448.3521222172001</v>
+        <v>645.3315754530863</v>
       </c>
       <c r="F41" t="n">
-        <v>254.5242144313295</v>
+        <v>451.5036676672158</v>
       </c>
       <c r="G41" t="n">
-        <v>61.84</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7405,19 +7405,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="M41" t="n">
-        <v>1673.704308114459</v>
+        <v>963.9979417665908</v>
       </c>
       <c r="N41" t="n">
-        <v>2286.924627889222</v>
+        <v>1577.218261541354</v>
       </c>
       <c r="O41" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947269</v>
       </c>
       <c r="P41" t="n">
         <v>2653.400904947332</v>
@@ -7435,19 +7435,19 @@
         <v>2391.593587515979</v>
       </c>
       <c r="U41" t="n">
-        <v>1950.966015244655</v>
+        <v>2391.593587515979</v>
       </c>
       <c r="V41" t="n">
-        <v>1529.904374672105</v>
+        <v>2232.983699381128</v>
       </c>
       <c r="W41" t="n">
-        <v>1100.234196913573</v>
+        <v>2232.983699381128</v>
       </c>
       <c r="X41" t="n">
-        <v>1079.844065237112</v>
+        <v>1849.870736289544</v>
       </c>
       <c r="Y41" t="n">
-        <v>1079.844065237112</v>
+        <v>1548.539996205901</v>
       </c>
     </row>
     <row r="42">
@@ -7490,34 +7490,34 @@
         <v>1278.949797864882</v>
       </c>
       <c r="M42" t="n">
-        <v>1575.900339607742</v>
+        <v>1538.705375336126</v>
       </c>
       <c r="N42" t="n">
-        <v>1920.05062421531</v>
+        <v>1882.855659943694</v>
       </c>
       <c r="O42" t="n">
-        <v>2369.963075899029</v>
+        <v>2332.768111627413</v>
       </c>
       <c r="P42" t="n">
-        <v>2521.804286309709</v>
+        <v>2656.167456096919</v>
       </c>
       <c r="Q42" t="n">
-        <v>2561.325813870134</v>
+        <v>2695.688983657344</v>
       </c>
       <c r="R42" t="n">
-        <v>2480.230476522543</v>
+        <v>2358.038683362011</v>
       </c>
       <c r="S42" t="n">
-        <v>2224.105224033037</v>
+        <v>2101.913430872505</v>
       </c>
       <c r="T42" t="n">
-        <v>2029.804451086053</v>
+        <v>1907.612657925521</v>
       </c>
       <c r="U42" t="n">
-        <v>1840.703077590915</v>
+        <v>1718.511284430383</v>
       </c>
       <c r="V42" t="n">
-        <v>1637.156949114632</v>
+        <v>1514.9651559541</v>
       </c>
       <c r="W42" t="n">
         <v>1415.567915872381</v>
@@ -7536,22 +7536,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="C43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="D43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="E43" t="n">
-        <v>77.77043040567538</v>
+        <v>61.84</v>
       </c>
       <c r="F43" t="n">
-        <v>77.77043040567538</v>
+        <v>61.84</v>
       </c>
       <c r="G43" t="n">
-        <v>77.77043040567538</v>
+        <v>61.84</v>
       </c>
       <c r="H43" t="n">
         <v>61.84</v>
@@ -7560,52 +7560,52 @@
         <v>61.84</v>
       </c>
       <c r="J43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="K43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="L43" t="n">
-        <v>98.52470713674859</v>
+        <v>61.84</v>
       </c>
       <c r="M43" t="n">
-        <v>98.52470713674859</v>
+        <v>61.84</v>
       </c>
       <c r="N43" t="n">
-        <v>98.52470713674859</v>
+        <v>61.84</v>
       </c>
       <c r="O43" t="n">
-        <v>98.52470713674859</v>
+        <v>61.84</v>
       </c>
       <c r="P43" t="n">
-        <v>98.52470713674859</v>
+        <v>61.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>98.52470713674859</v>
+        <v>61.84</v>
       </c>
       <c r="R43" t="n">
-        <v>98.52470713674859</v>
+        <v>61.84</v>
       </c>
       <c r="S43" t="n">
-        <v>98.52470713674859</v>
+        <v>61.84</v>
       </c>
       <c r="T43" t="n">
-        <v>98.52470713674859</v>
+        <v>61.84</v>
       </c>
       <c r="U43" t="n">
-        <v>159.9458997750352</v>
+        <v>61.84</v>
       </c>
       <c r="V43" t="n">
-        <v>159.9458997750352</v>
+        <v>61.84</v>
       </c>
       <c r="W43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="X43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="Y43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
     </row>
     <row r="44">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>61.84</v>
+        <v>363.6431836629652</v>
       </c>
       <c r="C44" t="n">
-        <v>61.84</v>
+        <v>98.51734705388037</v>
       </c>
       <c r="D44" t="n">
         <v>61.84</v>
@@ -7645,16 +7645,16 @@
         <v>453.1491130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>1218.419113037656</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="M44" t="n">
-        <v>1729.267941766591</v>
+        <v>963.9979417665908</v>
       </c>
       <c r="N44" t="n">
-        <v>2342.488261541354</v>
+        <v>1577.218261541354</v>
       </c>
       <c r="O44" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947255</v>
       </c>
       <c r="P44" t="n">
         <v>2653.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3092</v>
+        <v>3027.476162799703</v>
       </c>
       <c r="S44" t="n">
-        <v>2870.648037903025</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="T44" t="n">
-        <v>2466.935329086294</v>
+        <v>2312.8057087281</v>
       </c>
       <c r="U44" t="n">
-        <v>2000.045130552344</v>
+        <v>1845.91551019415</v>
       </c>
       <c r="V44" t="n">
-        <v>1552.720863717168</v>
+        <v>1398.591243358974</v>
       </c>
       <c r="W44" t="n">
-        <v>1096.788059696009</v>
+        <v>1398.591243358974</v>
       </c>
       <c r="X44" t="n">
-        <v>687.412470341799</v>
+        <v>989.2156540047641</v>
       </c>
       <c r="Y44" t="n">
-        <v>359.8191039955299</v>
+        <v>661.622287658495</v>
       </c>
     </row>
     <row r="45">
@@ -7718,43 +7718,43 @@
         <v>61.84</v>
       </c>
       <c r="J45" t="n">
-        <v>204.617202566286</v>
+        <v>370.9265201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>578.9400186606695</v>
+        <v>652.280438414683</v>
       </c>
       <c r="L45" t="n">
-        <v>1035.42048025587</v>
+        <v>1108.760900009883</v>
       </c>
       <c r="M45" t="n">
-        <v>1306.631021998729</v>
+        <v>1379.971441752742</v>
       </c>
       <c r="N45" t="n">
-        <v>1625.041306606297</v>
+        <v>1698.38172636031</v>
       </c>
       <c r="O45" t="n">
-        <v>2049.213758290016</v>
+        <v>2122.554178044029</v>
       </c>
       <c r="P45" t="n">
-        <v>2346.873102759523</v>
+        <v>2420.213522513536</v>
       </c>
       <c r="Q45" t="n">
-        <v>2360.654630319948</v>
+        <v>2420.213522513536</v>
       </c>
       <c r="R45" t="n">
-        <v>2343.930332204927</v>
+        <v>2420.213522513536</v>
       </c>
       <c r="S45" t="n">
-        <v>2343.930332204927</v>
+        <v>2420.213522513536</v>
       </c>
       <c r="T45" t="n">
-        <v>2123.366932995317</v>
+        <v>2199.650123303926</v>
       </c>
       <c r="U45" t="n">
-        <v>1908.002933237553</v>
+        <v>1984.286123546162</v>
       </c>
       <c r="V45" t="n">
-        <v>1678.194178498644</v>
+        <v>1754.477368807253</v>
       </c>
       <c r="W45" t="n">
         <v>1678.194178498644</v>
@@ -7773,22 +7773,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="C46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="D46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="E46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="F46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="G46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="H46" t="n">
         <v>61.84</v>
@@ -7797,52 +7797,52 @@
         <v>61.84</v>
       </c>
       <c r="J46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="K46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="L46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="M46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="N46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="O46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="P46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="Q46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="R46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="S46" t="n">
-        <v>143.672759546362</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="T46" t="n">
-        <v>120.4156216612533</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="U46" t="n">
-        <v>156.0968142995399</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="V46" t="n">
-        <v>143.8035716568973</v>
+        <v>61.84</v>
       </c>
       <c r="W46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="X46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="Y46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
     </row>
   </sheetData>
@@ -7964,10 +7964,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>214.2751174529344</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>716.8751175230994</v>
+        <v>500.8454983898776</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814674</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8204,22 +8204,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>202.8544162978924</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>884.2478695740924</v>
+        <v>668.2182504408672</v>
       </c>
       <c r="P5" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406851054</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8441,7 +8441,7 @@
         <v>51.24160624509022</v>
       </c>
       <c r="K8" t="n">
-        <v>65.90862873094417</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>884.2478695740924</v>
@@ -8459,7 +8459,7 @@
         <v>814.2870600406815</v>
       </c>
       <c r="Q8" t="n">
-        <v>615.8520732695737</v>
+        <v>584.3000488963706</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,10 +8678,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,7 +8690,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>602.7693615519817</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>148.8262285640457</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,7 +8927,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>602.7693615519817</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9149,13 +9149,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>148.8262285640457</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>231.79875049407</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9398,10 +9398,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>815.1849144666769</v>
       </c>
       <c r="O20" t="n">
-        <v>602.7693615519817</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
@@ -9629,16 +9629,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>815.1849144666769</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>602.7693615519817</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
@@ -9866,7 +9866,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>370.1780576344547</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,7 +9875,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>440.4259272085471</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
         <v>0.2870600406814136</v>
@@ -10100,19 +10100,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>772.9999999999999</v>
+        <v>773</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>1096.663422488788</v>
+        <v>693.8414801232425</v>
       </c>
       <c r="O29" t="n">
-        <v>384.3010447316466</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
@@ -10334,13 +10334,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>50.42570624509119</v>
       </c>
       <c r="K32" t="n">
-        <v>375.2922462381595</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>772.9999999999998</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10349,7 +10349,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>843.2478695741345</v>
+        <v>108.544028630255</v>
       </c>
       <c r="P32" t="n">
         <v>0.2870600406814136</v>
@@ -10571,13 +10571,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>50.42570624509131</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>375.2922462381517</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
@@ -10586,10 +10586,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>108.5440286302591</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407308</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10811,10 +10811,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>375.2922462381459</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10826,7 +10826,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407381</v>
+        <v>431.7041887557792</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,7 +11048,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11060,10 +11060,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>440.4259272085471</v>
+        <v>384.3010447315827</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407454</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11288,7 +11288,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11297,10 +11297,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>384.3010447316466</v>
+        <v>384.301044731568</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407599</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22706,7 +22706,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>29.21007785422989</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>29.21007785422643</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>5.6624496964466</v>
+        <v>5.66244969645156</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.662449696448633</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5.662449696442934</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23226,16 +23226,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>58.95976110113358</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>178.7573722870162</v>
@@ -23271,7 +23271,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>19.33752138217113</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -23283,7 +23283,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -23469,16 +23469,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>82.66357762404179</v>
+        <v>86.30994672070055</v>
       </c>
       <c r="G14" t="n">
         <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>157.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23657,16 +23657,16 @@
         <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>389.445564079015</v>
+        <v>335.7042833489048</v>
       </c>
       <c r="P16" t="n">
         <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>421.860847251041</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4306086145860206</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23897,13 +23897,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>69.04626797189979</v>
       </c>
       <c r="Q19" t="n">
-        <v>108.2004986247733</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -23937,7 +23937,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4306086145800521</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24371,13 +24371,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>69.04626797189979</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>108.2004986247733</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24408,10 +24408,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -24423,10 +24423,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>23.58082522918716</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>173.630683561505</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,10 +24459,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -24572,7 +24572,7 @@
         <v>47.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>55.98090483695654</v>
@@ -24596,13 +24596,13 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
         <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>203.9559039409364</v>
+        <v>346.1850752716849</v>
       </c>
       <c r="O28" t="n">
         <v>415.445564079015</v>
@@ -24614,10 +24614,10 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>358.7350262510344</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24648,22 +24648,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>35.06290239760591</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24705,10 +24705,10 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>348.1589027539205</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -25070,28 +25070,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>51.31795371660968</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
         <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>434.839266425598</v>
+        <v>1.322948915208713</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25307,25 +25307,25 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>51.31795371660968</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>396.4478973282775</v>
+        <v>326.3973665406075</v>
       </c>
       <c r="Q37" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>71.37347970285543</v>
@@ -25544,7 +25544,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>229.6316114025499</v>
@@ -25559,13 +25559,13 @@
         <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.322948915181712</v>
+        <v>62.49709737013251</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25611,7 +25611,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25650,19 +25650,19 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>259.8272349133212</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>359.0956031009714</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>298.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>253.9894133182643</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>120.9698752289262</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25760,7 +25760,7 @@
         <v>72.53621805555548</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>67.98090483695654</v>
       </c>
       <c r="F43" t="n">
         <v>61.38285596774193</v>
@@ -25769,7 +25769,7 @@
         <v>32.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>15.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25781,7 +25781,7 @@
         <v>75.52077380114304</v>
       </c>
       <c r="L43" t="n">
-        <v>72.67128497723348</v>
+        <v>210.5476281577792</v>
       </c>
       <c r="M43" t="n">
         <v>307.6316114025499</v>
@@ -25814,7 +25814,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>13.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>34.44364543010755</v>
@@ -25833,10 +25833,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>262.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>223.3391557398498</v>
+        <v>187.0285821565082</v>
       </c>
       <c r="E44" t="n">
         <v>217.3632896068686</v>
@@ -25878,10 +25878,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>88.70972532631805</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -25893,7 +25893,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -25957,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>343.7167421585088</v>
+        <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>279.5639999646113</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>169.8527845043057</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26006,7 +26006,7 @@
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26042,7 +26042,7 @@
         <v>175.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>23.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -26051,7 +26051,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>957915.3692042468</v>
+        <v>957915.3692042469</v>
       </c>
     </row>
     <row r="3">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7183934.939620385</v>
+        <v>7183934.939620387</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7907621.308234077</v>
+        <v>7907621.308234079</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8705879.448403807</v>
+        <v>8705879.448403809</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9502797.065307586</v>
+        <v>9502797.065307587</v>
       </c>
     </row>
     <row r="14">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11000460.23432512</v>
+        <v>11000460.23432511</v>
       </c>
     </row>
     <row r="16">
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1384543.598310502</v>
+        <v>1384543.598310503</v>
       </c>
       <c r="C2" t="n">
         <v>1384543.598310503</v>
       </c>
       <c r="D2" t="n">
-        <v>1384543.598310503</v>
+        <v>1384543.598310502</v>
       </c>
       <c r="E2" t="n">
         <v>1238631.925191176</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>575615.820517953</v>
+        <v>580502.372390945</v>
       </c>
       <c r="C4" t="n">
-        <v>573863.9117786936</v>
+        <v>578750.4636516855</v>
       </c>
       <c r="D4" t="n">
-        <v>572109.6264658829</v>
+        <v>576996.1783388748</v>
       </c>
       <c r="E4" t="n">
-        <v>493887.8206072089</v>
+        <v>498724.2862854869</v>
       </c>
       <c r="F4" t="n">
-        <v>518162.4364012047</v>
+        <v>522998.9020794826</v>
       </c>
       <c r="G4" t="n">
-        <v>542951.8445255277</v>
+        <v>547788.3102038058</v>
       </c>
       <c r="H4" t="n">
-        <v>541278.9095854309</v>
+        <v>546115.3752637085</v>
       </c>
       <c r="I4" t="n">
-        <v>539603.6392010038</v>
+        <v>544440.1048792817</v>
       </c>
       <c r="J4" t="n">
-        <v>483069.458967209</v>
+        <v>487781.687779115</v>
       </c>
       <c r="K4" t="n">
-        <v>481604.7173132672</v>
+        <v>486316.9461251733</v>
       </c>
       <c r="L4" t="n">
-        <v>543419.7365500293</v>
+        <v>548178.8299014302</v>
       </c>
       <c r="M4" t="n">
-        <v>541689.6178484766</v>
+        <v>546448.711199878</v>
       </c>
       <c r="N4" t="n">
-        <v>539957.0115239245</v>
+        <v>544716.1048753255</v>
       </c>
       <c r="O4" t="n">
-        <v>457615.9305970519</v>
+        <v>462328.1594089579</v>
       </c>
       <c r="P4" t="n">
-        <v>416810.1932019159</v>
+        <v>421522.422013822</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>439280.977792549</v>
+        <v>434394.425919558</v>
       </c>
       <c r="C6" t="n">
-        <v>727560.8865318091</v>
+        <v>722674.3346588174</v>
       </c>
       <c r="D6" t="n">
-        <v>729315.1718446205</v>
+        <v>724428.6199716274</v>
       </c>
       <c r="E6" t="n">
-        <v>496337.3795839673</v>
+        <v>491500.9139056893</v>
       </c>
       <c r="F6" t="n">
-        <v>679590.4293241625</v>
+        <v>674753.9636458849</v>
       </c>
       <c r="G6" t="n">
-        <v>702773.2963126287</v>
+        <v>697936.8306343503</v>
       </c>
       <c r="H6" t="n">
-        <v>726846.2312527259</v>
+        <v>722009.765574448</v>
       </c>
       <c r="I6" t="n">
-        <v>728521.5016371532</v>
+        <v>723685.0359588751</v>
       </c>
       <c r="J6" t="n">
-        <v>266820.6244559667</v>
+        <v>262108.3956440609</v>
       </c>
       <c r="K6" t="n">
-        <v>656381.366109909</v>
+        <v>651669.1372980028</v>
       </c>
       <c r="L6" t="n">
-        <v>658547.5976717463</v>
+        <v>653788.5043203454</v>
       </c>
       <c r="M6" t="n">
-        <v>735477.7163732992</v>
+        <v>730718.6230218976</v>
       </c>
       <c r="N6" t="n">
-        <v>737210.3226978516</v>
+        <v>732451.2293464502</v>
       </c>
       <c r="O6" t="n">
-        <v>591224.6384301251</v>
+        <v>586512.4096182192</v>
       </c>
       <c r="P6" t="n">
-        <v>628696.3875168273</v>
+        <v>623984.1587049206</v>
       </c>
     </row>
   </sheetData>
@@ -26993,7 +26993,7 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27436,55 +27436,55 @@
         <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>307.3903671255648</v>
+        <v>400</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>307.3903671255645</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>400</v>
-      </c>
-      <c r="G2" t="n">
-        <v>400</v>
-      </c>
-      <c r="H2" t="n">
-        <v>400</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>115.3536407070568</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -27575,7 +27575,7 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>342.2743756165772</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27591,34 +27591,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>372.5896814150759</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>206.4874075557077</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27648,19 +27648,19 @@
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27676,22 +27676,22 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>56.51176829727007</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>56.51176829727025</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27730,16 +27730,16 @@
         <v>400</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W5" t="n">
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -27797,7 +27797,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,16 +27806,16 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
+        <v>342.2743756165773</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>400</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>400</v>
-      </c>
-      <c r="X6" t="n">
-        <v>342.2743756165772</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27834,16 +27834,16 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F7" t="n">
         <v>400</v>
       </c>
-      <c r="F7" t="n">
-        <v>274.3828559677419</v>
-      </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>352.6345394581961</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27852,10 +27852,10 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>146.1585542514326</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,10 +27882,10 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
@@ -27907,19 +27907,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E8" t="n">
+        <v>307.3903671255648</v>
+      </c>
+      <c r="F8" t="n">
         <v>400</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,13 +27955,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>400</v>
-      </c>
-      <c r="T8" t="n">
-        <v>306.4306086145853</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27970,13 +27970,13 @@
         <v>400</v>
       </c>
       <c r="W8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -27989,13 +27989,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>251.3119749597993</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28043,13 +28043,13 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>275.152123820318</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28071,25 +28071,25 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>331.2709046696329</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>35.26894883590776</v>
+        <v>130.1091612565427</v>
       </c>
       <c r="K10" t="n">
         <v>288.520773801143</v>
@@ -28116,19 +28116,19 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28247,7 +28247,7 @@
         <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>225</v>
+        <v>19.11687125883891</v>
       </c>
       <c r="K12" t="n">
         <v>225</v>
@@ -28256,7 +28256,7 @@
         <v>225</v>
       </c>
       <c r="M12" t="n">
-        <v>19.1168712588388</v>
+        <v>225</v>
       </c>
       <c r="N12" t="n">
         <v>225</v>
@@ -28484,19 +28484,19 @@
         <v>251</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>166.1982915220773</v>
       </c>
       <c r="K15" t="n">
-        <v>166.1982915220773</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>251</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="N15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -28736,10 +28736,10 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
+        <v>279</v>
+      </c>
+      <c r="P18" t="n">
         <v>155.6705902671032</v>
-      </c>
-      <c r="P18" t="n">
-        <v>279</v>
       </c>
       <c r="Q18" t="n">
         <v>279</v>
@@ -28858,7 +28858,7 @@
         <v>279</v>
       </c>
       <c r="C20" t="n">
-        <v>279.000000000006</v>
+        <v>279</v>
       </c>
       <c r="D20" t="n">
         <v>279</v>
@@ -28958,10 +28958,10 @@
         <v>279</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>155.6705902671031</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -28973,10 +28973,10 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>155.6705902671032</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>279</v>
@@ -29444,13 +29444,13 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O27" t="n">
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29681,13 +29681,13 @@
         <v>225</v>
       </c>
       <c r="N30" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O30" t="n">
         <v>225</v>
       </c>
       <c r="P30" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q30" t="n">
         <v>225</v>
@@ -29912,7 +29912,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>227.0158611578289</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -29924,7 +29924,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>227.0158611578287</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>291</v>
@@ -29967,7 +29967,7 @@
         <v>291</v>
       </c>
       <c r="D34" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
       <c r="E34" t="n">
         <v>291</v>
@@ -30061,7 +30061,7 @@
         <v>291</v>
       </c>
       <c r="I35" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S35" t="n">
         <v>291</v>
@@ -30143,7 +30143,7 @@
         <v>291</v>
       </c>
       <c r="J36" t="n">
-        <v>227.015861157829</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30161,7 +30161,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>227.0158611578287</v>
       </c>
       <c r="Q36" t="n">
         <v>291</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
       <c r="C37" t="n">
         <v>291</v>
@@ -30267,7 +30267,7 @@
         <v>291</v>
       </c>
       <c r="Y37" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
     </row>
     <row r="38">
@@ -30283,7 +30283,7 @@
         <v>291</v>
       </c>
       <c r="D38" t="n">
-        <v>291</v>
+        <v>282.5434086145857</v>
       </c>
       <c r="E38" t="n">
         <v>291</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>242.4220074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30389,7 +30389,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>227.0158611578289</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -30398,10 +30398,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>291</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>227.0158611578289</v>
       </c>
       <c r="R39" t="n">
         <v>291</v>
@@ -30504,7 +30504,7 @@
         <v>291</v>
       </c>
       <c r="Y40" t="n">
-        <v>291.0000000000276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41">
@@ -30626,7 +30626,7 @@
         <v>213</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>175.4293290185695</v>
       </c>
       <c r="N42" t="n">
         <v>213</v>
@@ -30635,7 +30635,7 @@
         <v>213</v>
       </c>
       <c r="P42" t="n">
-        <v>39.70895549613474</v>
+        <v>213</v>
       </c>
       <c r="Q42" t="n">
         <v>213</v>
@@ -30696,7 +30696,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>213</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30729,7 +30729,7 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U43" t="n">
-        <v>213</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
         <v>199.1703102162162</v>
@@ -30854,10 +30854,10 @@
         <v>187</v>
       </c>
       <c r="J45" t="n">
-        <v>19.01079029392634</v>
+        <v>187</v>
       </c>
       <c r="K45" t="n">
-        <v>187</v>
+        <v>93.09202236868747</v>
       </c>
       <c r="L45" t="n">
         <v>187</v>
@@ -30875,7 +30875,7 @@
         <v>187</v>
       </c>
       <c r="Q45" t="n">
-        <v>187</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
         <v>187</v>
@@ -30933,7 +30933,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>117.9283019130411</v>
+        <v>47.68636564665789</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>187</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34877,34 +34877,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>91.60877657811932</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>29.85395193558944</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34934,19 +34934,19 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,7 +34983,7 @@
         <v>814</v>
       </c>
       <c r="K5" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -34998,7 +34998,7 @@
         <v>814</v>
       </c>
       <c r="P5" t="n">
-        <v>814</v>
+        <v>814.0000000000036</v>
       </c>
       <c r="Q5" t="n">
         <v>814</v>
@@ -35120,16 +35120,16 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>107.5906666166661</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35138,10 +35138,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>110.8896054155249</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,10 +35168,10 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -35220,7 +35220,7 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -35238,7 +35238,7 @@
         <v>814</v>
       </c>
       <c r="Q8" t="n">
-        <v>814.0000000000045</v>
+        <v>814</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35357,25 +35357,25 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>102.4997785680142</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>94.84021242063494</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35402,19 +35402,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35457,10 +35457,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230993</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,7 +35469,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>532.5214919778892</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35533,7 +35533,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965146</v>
       </c>
       <c r="K12" t="n">
         <v>416.1038546407913</v>
@@ -35542,7 +35542,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
-        <v>106.0669134233431</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N12" t="n">
         <v>359.6265501086548</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,7 +35706,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>532.5214919778892</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35770,19 +35770,19 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>291.406897759753</v>
       </c>
       <c r="K15" t="n">
-        <v>357.3021461628686</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
         <v>525.0913753486871</v>
       </c>
       <c r="M15" t="n">
-        <v>86.95004216450428</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>385.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
         <v>241.4570219027464</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>161.5508809199775</v>
+        <v>814</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36022,10 +36022,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>397.1276121698496</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>392.6660045146532</v>
+        <v>269.3365947817563</v>
       </c>
       <c r="Q18" t="n">
         <v>105.9207349095204</v>
@@ -36177,10 +36177,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>337.9359563968417</v>
       </c>
       <c r="O20" t="n">
-        <v>532.5214919778892</v>
+        <v>814</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36244,10 +36244,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>191.1038546407913</v>
+        <v>346.7744449078945</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
@@ -36259,10 +36259,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>397.1276121698496</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
         <v>105.9207349095204</v>
@@ -36408,16 +36408,16 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>337.9359563968417</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>532.5214919778892</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36645,7 +36645,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>370.1780576344547</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,7 +36654,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>370.1780576344547</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36730,13 +36730,13 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O27" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36879,19 +36879,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>772.9999999999999</v>
+        <v>773</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>619.4144644189528</v>
+        <v>216.5925220534073</v>
       </c>
       <c r="O29" t="n">
-        <v>314.0531751575541</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -36967,13 +36967,13 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O30" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
         <v>51.92073490952041</v>
@@ -37116,7 +37116,7 @@
         <v>773.0000000000421</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320763032</v>
+        <v>727.1079320760333</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
@@ -37198,7 +37198,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>274.091375348687</v>
+        <v>501.1072365065158</v>
       </c>
       <c r="M33" t="n">
         <v>86.95004216450428</v>
@@ -37210,7 +37210,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>340.6818656724819</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>117.9207349095204</v>
@@ -37253,7 +37253,7 @@
         <v>18.27475335195533</v>
       </c>
       <c r="D34" t="n">
-        <v>5.463781944468437</v>
+        <v>5.46378194444452</v>
       </c>
       <c r="E34" t="n">
         <v>10.01909516304346</v>
@@ -37353,7 +37353,7 @@
         <v>773.0000000000493</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320762573</v>
+        <v>727.1079320762591</v>
       </c>
       <c r="L35" t="n">
         <v>773</v>
@@ -37429,7 +37429,7 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J36" t="n">
-        <v>352.2244673955047</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K36" t="n">
         <v>191.1038546407913</v>
@@ -37447,7 +37447,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>113.6660045146532</v>
+        <v>340.6818656724819</v>
       </c>
       <c r="Q36" t="n">
         <v>117.9207349095204</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.886199662945266</v>
+        <v>3.886199662921342</v>
       </c>
       <c r="C37" t="n">
         <v>18.27475335195533</v>
@@ -37553,7 +37553,7 @@
         <v>43.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.534647150537637</v>
+        <v>3.534647150561582</v>
       </c>
     </row>
     <row r="38">
@@ -37590,10 +37590,10 @@
         <v>773.0000000000566</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320762788</v>
+        <v>773.0000000000002</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>727.1079320759846</v>
       </c>
       <c r="M38" t="n">
         <v>773.0000000000566</v>
@@ -37675,7 +37675,7 @@
         <v>274.091375348687</v>
       </c>
       <c r="M39" t="n">
-        <v>86.95004216450428</v>
+        <v>313.9659033223331</v>
       </c>
       <c r="N39" t="n">
         <v>134.6265501086548</v>
@@ -37684,10 +37684,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>404.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
-        <v>53.9365960673493</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37790,7 +37790,7 @@
         <v>43.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.53464715056522</v>
+        <v>3.534647150537637</v>
       </c>
     </row>
     <row r="41">
@@ -37827,7 +37827,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -37839,10 +37839,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>370.1780576344547</v>
+        <v>314.0531751574902</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>773.0000000000639</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37912,7 +37912,7 @@
         <v>487.091375348687</v>
       </c>
       <c r="M42" t="n">
-        <v>299.9500421645043</v>
+        <v>262.3793711830738</v>
       </c>
       <c r="N42" t="n">
         <v>347.6265501086548</v>
@@ -37921,7 +37921,7 @@
         <v>454.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>153.374960010788</v>
+        <v>326.6660045146532</v>
       </c>
       <c r="Q42" t="n">
         <v>39.92073490952041</v>
@@ -37982,7 +37982,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>177.7310511640922</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>62.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38067,7 +38067,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38076,10 +38076,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>314.0531751575541</v>
+        <v>314.0531751574756</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>773.0000000000784</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38140,10 +38140,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>144.2193965316021</v>
+        <v>312.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>378.1038546407913</v>
+        <v>284.1958770094788</v>
       </c>
       <c r="L45" t="n">
         <v>461.091375348687</v>
@@ -38161,7 +38161,7 @@
         <v>300.6660045146532</v>
       </c>
       <c r="Q45" t="n">
-        <v>13.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>82.65935307713337</v>
+        <v>12.41741681075013</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>36.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
